--- a/transformers/experiments/1d_resnet/summary.xlsx
+++ b/transformers/experiments/1d_resnet/summary.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J12"/>
+  <dimension ref="A1:J14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -842,6 +842,74 @@
         <v>0.002763234438627106</v>
       </c>
     </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>epochs_50</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>32</v>
+      </c>
+      <c r="C13" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="E13" t="n">
+        <v>50</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0.9613147178592205</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0.9634962187318208</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0.9562245491564864</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0.9603451619158425</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0.003731531005996833</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>epochs_100</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>32</v>
+      </c>
+      <c r="C14" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="D14" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="E14" t="n">
+        <v>100</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0.9613147178592205</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0.962914485165794</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0.9562245491564864</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0.960151250727167</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0.003493429944579474</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
